--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,16 +808,28 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8734,0.0379,0.0009,0.0193</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.9694,0.0010,0.0008,0.0183</t>
-  </si>
-  <si>
-    <t>0.0009,0.0054,0.0007,0.9989</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9860,0.0016,0.0027,0.0022</t>
+  </si>
+  <si>
+    <t>0.0125,0.0000,0.0000,0.9985</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0126,0.0004,0.0001,0.9967</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
@@ -829,679 +841,661 @@
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0000</t>
+    <t>0.9995,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0025,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0019,0.9915,0.0004</t>
-  </si>
-  <si>
-    <t>0.0685,0.0025,0.9385,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0001,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0001,0.0012,0.0001</t>
+    <t>0.9924,0.0002,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.0376,0.0001,0.9739,0.0001</t>
+  </si>
+  <si>
+    <t>0.4624,0.0030,0.5366,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0001,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9982,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.6248,0.0006,0.3804,0.0015</t>
+  </si>
+  <si>
+    <t>0.9924,0.0001,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0231,0.0002,0.9821,0.0001</t>
+  </si>
+  <si>
+    <t>0.7554,0.0000,0.4578,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9995,0.0013</t>
+  </si>
+  <si>
+    <t>0.7834,0.3137,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,0.9999,0.0108</t>
+  </si>
+  <si>
+    <t>0.0016,0.9920,0.0186,0.0000</t>
+  </si>
+  <si>
+    <t>0.9827,0.0086,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.0099,0.0026,0.9854,0.0019</t>
+  </si>
+  <si>
+    <t>0.1156,0.8658,0.0137,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9965,0.1092,0.0000</t>
+  </si>
+  <si>
+    <t>0.0072,0.0100,0.9697,0.0011</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0107,0.0003,0.9862,0.0002</t>
+  </si>
+  <si>
+    <t>0.0228,0.0000,0.9710,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0002,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9906,0.0018,0.1427</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9991,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.6480,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0020,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0068,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0022,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0012</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0022,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9921,0.9070,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9951,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.2019,0.0066,0.7424,0.0015</t>
+  </si>
+  <si>
+    <t>0.0105,0.0016,0.9857,0.0017</t>
+  </si>
+  <si>
+    <t>0.0000,0.9881,0.9955,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.6963,0.9671,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0930,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.8099,0.0000</t>
+  </si>
+  <si>
+    <t>0.0386,0.0000,0.0002,0.9899</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0056,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0005,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9884,0.9839,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9644,0.9872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9100,0.5317,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9946,0.4198,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.8963,0.4201,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9891,0.0161,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0023,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9951,0.0026,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0011,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.0019,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9546,0.0000,0.0958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9995,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9980,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0172,0.0006,0.9754,0.0008</t>
-  </si>
-  <si>
-    <t>0.9275,0.0008,0.0795,0.0010</t>
+    <t>0.0144,0.9817,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0065,0.9900,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8979,0.1238,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9849,0.0013,0.0042,0.0011</t>
+  </si>
+  <si>
+    <t>0.0990,0.0001,0.9060,0.0005</t>
+  </si>
+  <si>
+    <t>0.9760,0.0059,0.0041,0.0001</t>
+  </si>
+  <si>
+    <t>0.9670,0.0013,0.0214,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.2043,0.0001,0.9886</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.9215,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.5709,0.3825,0.0091,0.0003</t>
+  </si>
+  <si>
+    <t>0.5052,0.5623,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7056,0.9917,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.8105,0.5778,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0005,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.9279,0.0007,0.0687,0.0003</t>
+  </si>
+  <si>
+    <t>0.0941,0.0000,0.9444,0.0001</t>
+  </si>
+  <si>
+    <t>0.9714,0.0006,0.0237,0.0001</t>
+  </si>
+  <si>
+    <t>0.0509,0.0000,0.0001,0.9888</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9510,0.9904,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9954,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.1028,0.8756,0.0072,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0955,0.0000,0.0018,0.9254</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0057,0.9977,0.0109</t>
+  </si>
+  <si>
+    <t>0.9969,0.0001,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.9836,0.0013,0.0063,0.0006</t>
+  </si>
+  <si>
+    <t>0.0760,0.8238,0.0300,0.0007</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9857,0.0099,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9410,0.0246,0.0127,0.0005</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0020,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.4264,0.3566,0.0001,0.0025</t>
+  </si>
+  <si>
+    <t>0.5697,0.4844,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.8588,0.2174,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1689,0.0023,0.8688,0.0007</t>
+  </si>
+  <si>
+    <t>0.9358,0.0417,0.0096,0.0018</t>
+  </si>
+  <si>
+    <t>0.9934,0.0052,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0028,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9915,0.0022,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0058,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.5806,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0146,0.0002,0.9890,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0012,0.9958,0.0002</t>
+  </si>
+  <si>
+    <t>0.6400,0.0005,0.3774,0.0006</t>
+  </si>
+  <si>
+    <t>0.5333,0.1023,0.0804,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.7978,0.3807,0.0013</t>
+  </si>
+  <si>
+    <t>0.9800,0.0005,0.0161,0.0001</t>
+  </si>
+  <si>
+    <t>0.7272,0.0006,0.3208,0.0006</t>
+  </si>
+  <si>
+    <t>0.9198,0.0022,0.0612,0.0004</t>
+  </si>
+  <si>
+    <t>0.0062,0.9932,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8060,0.2974,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8568,0.1711,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.7248,0.3668,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0017,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0000,0.0050,0.0000</t>
+  </si>
+  <si>
+    <t>0.9424,0.0037,0.0207,0.0053</t>
+  </si>
+  <si>
+    <t>0.8882,0.0024,0.1247,0.0002</t>
+  </si>
+  <si>
+    <t>0.5504,0.0002,0.5683,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.0002,0.9975,0.0005</t>
+  </si>
+  <si>
+    <t>0.0064,0.0003,0.9903,0.0003</t>
+  </si>
+  <si>
+    <t>0.0345,0.0019,0.9644,0.0001</t>
+  </si>
+  <si>
+    <t>0.0263,0.0008,0.9711,0.0004</t>
+  </si>
+  <si>
+    <t>0.0248,0.0750,0.8439,0.0011</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9811,0.0183,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9966,0.0025,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0014,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.2073,0.0249,0.6623,0.0009</t>
+  </si>
+  <si>
+    <t>0.9872,0.0003,0.0045,0.0018</t>
   </si>
   <si>
     <t>0.0003,0.0000,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0592,0.0011,0.9498,0.0001</t>
-  </si>
-  <si>
-    <t>0.0547,0.0000,0.9638,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.0000,0.9809,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9996,0.0010</t>
-  </si>
-  <si>
-    <t>0.0769,0.9561,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0030,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.9999,0.0055</t>
-  </si>
-  <si>
-    <t>0.0019,0.9747,0.0588,0.0001</t>
-  </si>
-  <si>
-    <t>0.9925,0.0019,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0131,0.0009,0.9802,0.0063</t>
-  </si>
-  <si>
-    <t>0.4665,0.4336,0.0261,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9946,0.0478,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0064,0.9841,0.0007</t>
-  </si>
-  <si>
-    <t>0.0035,0.0049,0.9922,0.0011</t>
-  </si>
-  <si>
-    <t>0.0226,0.0097,0.9599,0.0002</t>
-  </si>
-  <si>
-    <t>0.0023,0.0000,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0002,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9977,0.0008,0.0188</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9989,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0158,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0106,0.0000,0.9901,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0015,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.9922,0.0060,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9894,0.0130,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9996,0.0014</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.7561,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0039,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9894,0.9911,0.0000</t>
+    <t>0.0000,0.0006,0.9998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.4109,0.9958,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0020,0.9941,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0010,0.9983,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0002,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.9748,0.0063,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.0052,0.0004,0.9924,0.0028</t>
-  </si>
-  <si>
-    <t>0.0000,0.9809,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.6525,0.9805,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.4430,0.0000</t>
-  </si>
-  <si>
-    <t>0.0337,0.0001,0.0011,0.9854</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0004,0.9998</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0008,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9893,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9596,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.1848,0.9910,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.7372,0.9899,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9836,0.9785,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9963,0.5870,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0259,0.9669,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.0039,0.9925,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9988,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.3590,0.6859,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9304,0.0023,0.0304,0.0020</t>
-  </si>
-  <si>
-    <t>0.6388,0.0001,0.4544,0.0003</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.0011,0.0002,0.9982</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9755,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.9969,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9732,0.0237,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9509,0.0693,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.7808,0.9662,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.4090,0.9901,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.2457,0.0019,0.7093,0.0016</t>
-  </si>
-  <si>
-    <t>0.0838,0.0000,0.9539,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2967,0.0000,0.0000,0.9197</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0011,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.9773,0.8801,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0676,0.9089,0.0059,0.0029</t>
-  </si>
-  <si>
-    <t>0.6710,0.3539,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.8244,0.0000,0.0037,0.1574</t>
-  </si>
-  <si>
-    <t>0.0010,0.0085,0.9980,0.0045</t>
-  </si>
-  <si>
-    <t>0.9959,0.0000,0.0006,0.0030</t>
-  </si>
-  <si>
-    <t>0.9760,0.0002,0.0123,0.0011</t>
-  </si>
-  <si>
-    <t>0.8453,0.2393,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0015,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8360,0.0401,0.0249,0.0002</t>
-  </si>
-  <si>
-    <t>0.9802,0.0158,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0006,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9873,0.0066,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9926,0.0050,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.8842,0.0696,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.0602,0.9570,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.2933,0.7757,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9451,0.0005,0.0585,0.0003</t>
-  </si>
-  <si>
-    <t>0.9673,0.0315,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0035,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.4729,0.5628,0.0037,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0133,0.0033,0.9837,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0213,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0006</t>
-  </si>
-  <si>
-    <t>0.0568,0.0012,0.9471,0.0001</t>
-  </si>
-  <si>
-    <t>0.0047,0.0017,0.9933,0.0004</t>
-  </si>
-  <si>
-    <t>0.0127,0.0022,0.9820,0.0004</t>
-  </si>
-  <si>
-    <t>0.1961,0.0879,0.4268,0.0005</t>
-  </si>
-  <si>
-    <t>0.0023,0.7334,0.4240,0.0015</t>
-  </si>
-  <si>
-    <t>0.0764,0.0020,0.9420,0.0002</t>
-  </si>
-  <si>
-    <t>0.3716,0.0012,0.5859,0.0037</t>
-  </si>
-  <si>
-    <t>0.1745,0.0002,0.8454,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.9888,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9987,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.6202,0.4226,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.0340,0.9654,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.4176,0.6750,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9250,0.0145,0.0203,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0000,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.9885,0.0006,0.0027,0.0011</t>
-  </si>
-  <si>
-    <t>0.9743,0.0012,0.0158,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0001,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.0087,0.0005,0.9855,0.0046</t>
-  </si>
-  <si>
-    <t>0.0303,0.0007,0.9608,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0901,0.0021,0.9229,0.0002</t>
-  </si>
-  <si>
-    <t>0.0042,0.8498,0.2392,0.0009</t>
-  </si>
-  <si>
-    <t>0.9964,0.0012,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9955,0.0019,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9850,0.0169,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0061,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9993,0.0007</t>
-  </si>
-  <si>
-    <t>0.5602,0.0595,0.1494,0.0006</t>
-  </si>
-  <si>
-    <t>0.9838,0.0002,0.0080,0.0031</t>
-  </si>
-  <si>
-    <t>0.0150,0.0006,0.9869,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1669,0.9921,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.9989,0.0008</t>
-  </si>
-  <si>
-    <t>0.0081,0.0033,0.9840,0.0006</t>
-  </si>
-  <si>
-    <t>0.9850,0.0000,0.0215,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0000,0.0031,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0001,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0042,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9803,0.0274,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9985,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0019,0.9962,0.0003</t>
-  </si>
-  <si>
-    <t>0.0189,0.2290,0.5480,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.9461,0.0001,0.0521,0.0012</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.9965,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9984,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0727,0.0004,0.0000,0.9729</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.0043,0.9971</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
+    <t>0.0002,0.0008,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0083,0.0090,0.9804,0.0010</t>
+  </si>
+  <si>
+    <t>0.9956,0.0000,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0000,0.0032,0.0000</t>
+  </si>
+  <si>
+    <t>0.2599,0.0004,0.7620,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0033,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0013,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9551,0.0285,0.0078,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0034,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0008,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0008,0.9967,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.1221,0.8324,0.0007</t>
+  </si>
+  <si>
+    <t>0.8816,0.0001,0.1255,0.0019</t>
+  </si>
+  <si>
+    <t>0.0018,0.0000,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.9665,0.0000,0.0007,0.0480</t>
+  </si>
+  <si>
+    <t>0.0015,0.0017,0.0000,0.9993</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0055,0.9977</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9771,0.0002,0.0015,0.0128</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1901,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1915,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1929,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1943,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1957,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1971,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1985,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1999,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2013,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2027,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2041,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2055,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2083,7 +2077,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2097,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2111,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2125,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2139,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2153,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2167,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2181,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2209,7 +2203,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2223,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2237,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,10 +2242,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2279,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2307,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2321,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2335,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2349,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2363,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2391,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2405,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2419,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2433,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2461,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2475,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2489,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2503,7 +2497,7 @@
         <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2517,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2531,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2545,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2559,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,10 +2564,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2587,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2601,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2615,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2629,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2643,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2657,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2671,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2685,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2699,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2713,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2727,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2741,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2755,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2769,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2783,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2797,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2825,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2839,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,10 +2844,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2867,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2881,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,7 +2889,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2909,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2920,10 +2914,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2937,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2951,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2965,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2979,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2993,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3007,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3021,7 +3015,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3035,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3046,10 +3040,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,10 +3068,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3088,10 +3082,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3105,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3119,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3133,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3147,7 +3141,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3161,7 +3155,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3175,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>268</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3189,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3203,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3217,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3231,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3245,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3259,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3273,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3287,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3301,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3315,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3329,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3343,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3357,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,10 +3362,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3385,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3399,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3413,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3427,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3441,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3455,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,10 +3460,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3483,7 +3477,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,10 +3488,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,7 +3505,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,7 +3519,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3539,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3553,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3567,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3581,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3595,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3609,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3623,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3634,10 +3628,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3651,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3665,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>273</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3679,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3693,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3707,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3721,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3735,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3749,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>273</v>
+        <v>360</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,7 +3757,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,10 +3768,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3791,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3805,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3819,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>379</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,10 +3824,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3847,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3861,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3889,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3903,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>346</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3917,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3931,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3945,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3959,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3973,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>351</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,10 +3978,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4001,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4012,10 +4006,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4029,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>273</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4043,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4057,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4071,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,10 +4076,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4099,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4113,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4127,7 +4121,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4141,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4155,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4169,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4183,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4197,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4211,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4225,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4239,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4253,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4267,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>383</v>
+        <v>418</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,10 +4272,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,10 +4286,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,10 +4300,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4320,10 +4314,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4337,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4351,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4365,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>421</v>
+        <v>356</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4393,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4407,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4421,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4435,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4449,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,10 +4454,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4477,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4491,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>312</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4505,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4519,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4533,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,10 +4538,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4561,7 +4555,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4575,7 +4569,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4586,10 +4580,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4614,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4631,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4645,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4659,7 +4653,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4670,10 +4664,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4701,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4715,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4729,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4743,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,10 +4748,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4771,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4785,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4799,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4813,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4841,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4855,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>455</v>
+        <v>412</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4869,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4883,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>457</v>
+        <v>414</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4897,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4911,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4925,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4939,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>461</v>
+        <v>277</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4964,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>463</v>
@@ -5037,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>468</v>
+        <v>331</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5051,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5065,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5079,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5093,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5107,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5121,7 +5115,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,10 +5126,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D234" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5149,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5163,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5177,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5191,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5205,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>480</v>
+        <v>277</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5219,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>354</v>
+        <v>479</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5233,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5247,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5261,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5275,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5303,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5317,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5345,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5359,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5387,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5401,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5415,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>494</v>
+        <v>342</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5429,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5443,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
